--- a/data/trans_orig/IP18A02-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP18A02-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17020</t>
+          <t>16979</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28090</t>
+          <t>27856</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9133</t>
+          <t>9419</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20021</t>
+          <t>19211</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29105</t>
+          <t>28850</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43684</t>
+          <t>44092</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>43,12%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22151</t>
+          <t>22385</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33221</t>
+          <t>33262</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31996</t>
+          <t>32806</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42884</t>
+          <t>42598</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58574</t>
+          <t>58166</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>73153</t>
+          <t>73408</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,79%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6748</t>
+          <t>6777</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16263</t>
+          <t>16491</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9223</t>
+          <t>9846</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20714</t>
+          <t>21089</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18851</t>
+          <t>19225</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34510</t>
+          <t>33590</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>17,85%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>75287</t>
+          <t>75059</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>84802</t>
+          <t>84773</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>75958</t>
+          <t>75583</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>87449</t>
+          <t>86826</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>153712</t>
+          <t>154632</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>169371</t>
+          <t>168997</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,79%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7433</t>
+          <t>8113</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17951</t>
+          <t>18743</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20568</t>
+          <t>20593</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20232</t>
+          <t>20596</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35898</t>
+          <t>35298</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,05%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45400</t>
+          <t>44608</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55918</t>
+          <t>55238</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46584</t>
+          <t>46559</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>94605</t>
+          <t>95205</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>110271</t>
+          <t>109907</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,22%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10841</t>
+          <t>10406</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21541</t>
+          <t>21655</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>9264</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19718</t>
+          <t>20053</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22724</t>
+          <t>22312</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38446</t>
+          <t>38282</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,32%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45855</t>
+          <t>45741</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>56555</t>
+          <t>56990</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48055</t>
+          <t>47720</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>58773</t>
+          <t>58509</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>96723</t>
+          <t>96887</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>112445</t>
+          <t>112857</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,49%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3676</t>
+          <t>3675</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11275</t>
+          <t>10997</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3546</t>
+          <t>3558</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11326</t>
+          <t>11819</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8877</t>
+          <t>9294</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19831</t>
+          <t>20157</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>31,36%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20834</t>
+          <t>21112</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28433</t>
+          <t>28434</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20839</t>
+          <t>20346</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28619</t>
+          <t>28607</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>44444</t>
+          <t>44118</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55398</t>
+          <t>54981</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>85,54%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6203</t>
+          <t>5978</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15599</t>
+          <t>15585</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6002</t>
+          <t>5851</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15045</t>
+          <t>14756</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14345</t>
+          <t>14027</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27056</t>
+          <t>27194</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,68%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>35508</t>
+          <t>35522</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>44904</t>
+          <t>45129</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35765</t>
+          <t>36054</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>44808</t>
+          <t>44959</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>74861</t>
+          <t>74723</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>87572</t>
+          <t>87890</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,24%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25850</t>
+          <t>25821</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40925</t>
+          <t>41649</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20293</t>
+          <t>20721</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35116</t>
+          <t>36733</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>50782</t>
+          <t>50362</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>72577</t>
+          <t>72801</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,66%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>80696</t>
+          <t>79972</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>95771</t>
+          <t>95800</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>88733</t>
+          <t>87116</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>103556</t>
+          <t>103128</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>172894</t>
+          <t>172670</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>194689</t>
+          <t>195109</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,48%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21324</t>
+          <t>20775</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>35313</t>
+          <t>35193</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17333</t>
+          <t>17147</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>32038</t>
+          <t>31262</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>42393</t>
+          <t>41843</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>62345</t>
+          <t>61751</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,29%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>85329</t>
+          <t>85449</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>99318</t>
+          <t>99867</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>101537</t>
+          <t>102313</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>116242</t>
+          <t>116428</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>191872</t>
+          <t>192466</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>211824</t>
+          <t>212374</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,54%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>123195</t>
+          <t>123311</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>157361</t>
+          <t>156291</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>111383</t>
+          <t>110984</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>143189</t>
+          <t>143305</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>241130</t>
+          <t>245853</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>288357</t>
+          <t>292357</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,92%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>440657</t>
+          <t>441727</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>474823</t>
+          <t>474707</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>480825</t>
+          <t>480709</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>512631</t>
+          <t>513030</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>933675</t>
+          <t>929675</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>980902</t>
+          <t>976179</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>79,88%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3962</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11590</t>
+          <t>11471</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4086</t>
+          <t>4455</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13444</t>
+          <t>13709</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9494</t>
+          <t>9668</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21693</t>
+          <t>21894</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37599</t>
+          <t>37718</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45227</t>
+          <t>45413</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41469</t>
+          <t>41204</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50827</t>
+          <t>50458</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>82409</t>
+          <t>82208</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>94608</t>
+          <t>94434</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,71%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7851</t>
+          <t>8165</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18975</t>
+          <t>19494</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>5987</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16761</t>
+          <t>15897</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16565</t>
+          <t>16027</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30754</t>
+          <t>31088</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>76308</t>
+          <t>75789</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>87432</t>
+          <t>87118</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>81372</t>
+          <t>82236</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>91623</t>
+          <t>92146</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>162662</t>
+          <t>162328</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>176851</t>
+          <t>177389</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,71%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11427</t>
+          <t>10993</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23483</t>
+          <t>22864</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8319</t>
+          <t>8185</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18400</t>
+          <t>19021</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20924</t>
+          <t>21311</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37235</t>
+          <t>36820</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,55%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43931</t>
+          <t>44550</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55987</t>
+          <t>56421</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52854</t>
+          <t>52233</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62935</t>
+          <t>63069</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>101433</t>
+          <t>101848</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>117744</t>
+          <t>117357</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,63%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6437</t>
+          <t>6945</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17051</t>
+          <t>16646</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2612</t>
+          <t>2602</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9880</t>
+          <t>10297</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10887</t>
+          <t>11098</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23652</t>
+          <t>23574</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,55%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>55283</t>
+          <t>55688</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>65897</t>
+          <t>65389</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>69349</t>
+          <t>68932</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76617</t>
+          <t>76627</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>127911</t>
+          <t>127989</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>140676</t>
+          <t>140465</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,68%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>665</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6221</t>
+          <t>6236</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14184</t>
+          <t>14425</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6701</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17634</t>
+          <t>17196</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,0%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32388</t>
+          <t>32373</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37948</t>
+          <t>37944</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29095</t>
+          <t>28854</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38313</t>
+          <t>38194</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>64254</t>
+          <t>64692</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>75187</t>
+          <t>75197</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,83%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9505</t>
+          <t>9165</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20002</t>
+          <t>19777</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5093</t>
+          <t>5139</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15096</t>
+          <t>14782</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16475</t>
+          <t>16651</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31494</t>
+          <t>31610</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,0%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33829</t>
+          <t>34054</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>44326</t>
+          <t>44666</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>43984</t>
+          <t>44298</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>53987</t>
+          <t>53941</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>81418</t>
+          <t>81302</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>96437</t>
+          <t>96261</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,25%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28725</t>
+          <t>29375</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45249</t>
+          <t>45574</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28121</t>
+          <t>28175</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44769</t>
+          <t>45270</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>61437</t>
+          <t>59732</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>85194</t>
+          <t>82266</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>29,58%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>89771</t>
+          <t>89446</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>106295</t>
+          <t>105645</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>98337</t>
+          <t>97836</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>114985</t>
+          <t>114931</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>192932</t>
+          <t>195860</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>216689</t>
+          <t>218394</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>78,52%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31823</t>
+          <t>32076</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>48517</t>
+          <t>49461</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>34335</t>
+          <t>33971</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>52483</t>
+          <t>53577</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>70974</t>
+          <t>71911</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>96031</t>
+          <t>97530</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>31,24%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>102860</t>
+          <t>101916</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>119554</t>
+          <t>119301</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>108339</t>
+          <t>107245</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>126487</t>
+          <t>126851</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>216168</t>
+          <t>214669</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>241225</t>
+          <t>240288</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>76,97%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>121942</t>
+          <t>122091</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>157901</t>
+          <t>157209</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>115941</t>
+          <t>116359</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>151303</t>
+          <t>152330</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>251680</t>
+          <t>250288</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>301133</t>
+          <t>300829</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,91%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>505156</t>
+          <t>505848</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>541115</t>
+          <t>540966</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>558512</t>
+          <t>557485</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>593874</t>
+          <t>593456</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1071739</t>
+          <t>1072043</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1121192</t>
+          <t>1122584</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,77%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3736</t>
+          <t>3808</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10884</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8054</t>
+          <t>7934</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18318</t>
+          <t>18182</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13555</t>
+          <t>13562</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26669</t>
+          <t>26269</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,22%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42070</t>
+          <t>41733</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49218</t>
+          <t>49146</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37198</t>
+          <t>37334</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47462</t>
+          <t>47582</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>81801</t>
+          <t>82201</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>94915</t>
+          <t>94908</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5793</t>
+          <t>6127</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15740</t>
+          <t>16813</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8708</t>
+          <t>9217</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19378</t>
+          <t>20193</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17477</t>
+          <t>17484</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31949</t>
+          <t>32998</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,32%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>71985</t>
+          <t>70912</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>81932</t>
+          <t>81598</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>73022</t>
+          <t>72207</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>83692</t>
+          <t>83183</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>148176</t>
+          <t>147127</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>162648</t>
+          <t>162641</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,29%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>8376</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18180</t>
+          <t>18822</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2218</t>
+          <t>2636</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10147</t>
+          <t>10098</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12460</t>
+          <t>12637</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25795</t>
+          <t>25370</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47051</t>
+          <t>46409</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57607</t>
+          <t>56855</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52651</t>
+          <t>52700</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60580</t>
+          <t>60162</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>102234</t>
+          <t>102659</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>115569</t>
+          <t>115392</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,13%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7284</t>
+          <t>7221</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18256</t>
+          <t>18380</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4042</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13333</t>
+          <t>13555</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14002</t>
+          <t>14312</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27861</t>
+          <t>28250</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,62%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>54361</t>
+          <t>54237</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>65333</t>
+          <t>65396</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>65802</t>
+          <t>65580</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>75093</t>
+          <t>75289</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>123891</t>
+          <t>123502</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>137750</t>
+          <t>137440</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,57%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6833</t>
+          <t>7092</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16524</t>
+          <t>16423</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9038</t>
+          <t>9044</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19479</t>
+          <t>18707</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18508</t>
+          <t>18729</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31634</t>
+          <t>33050</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>38,12%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25285</t>
+          <t>25386</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34976</t>
+          <t>34717</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25403</t>
+          <t>26175</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35844</t>
+          <t>35838</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>55058</t>
+          <t>53642</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>68184</t>
+          <t>67963</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>78,4%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3927</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11950</t>
+          <t>12422</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>3748</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13161</t>
+          <t>12333</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9858</t>
+          <t>10113</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21523</t>
+          <t>21768</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,04%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39630</t>
+          <t>39158</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47653</t>
+          <t>47649</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>43863</t>
+          <t>44691</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>52694</t>
+          <t>53276</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>87081</t>
+          <t>86836</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>98746</t>
+          <t>98491</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,69%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22156</t>
+          <t>21139</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>36327</t>
+          <t>35699</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24698</t>
+          <t>24762</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39873</t>
+          <t>40097</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>49537</t>
+          <t>49758</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>71144</t>
+          <t>71757</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>32,04%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>75219</t>
+          <t>75847</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>89390</t>
+          <t>90407</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>72558</t>
+          <t>72334</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>87733</t>
+          <t>87669</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>152833</t>
+          <t>152220</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>174440</t>
+          <t>174219</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>77,78%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25551</t>
+          <t>26020</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42827</t>
+          <t>42145</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>29418</t>
+          <t>29687</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>46479</t>
+          <t>47219</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>59700</t>
+          <t>60054</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>84247</t>
+          <t>83354</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>25,76%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>114980</t>
+          <t>115662</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>132256</t>
+          <t>131787</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>119253</t>
+          <t>118513</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>136314</t>
+          <t>136045</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>239292</t>
+          <t>240185</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>263839</t>
+          <t>263485</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,44%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>106202</t>
+          <t>106331</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>137208</t>
+          <t>139069</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>115814</t>
+          <t>113675</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>147761</t>
+          <t>147131</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>229916</t>
+          <t>231019</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>277317</t>
+          <t>277629</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,17%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>504061</t>
+          <t>502200</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>535067</t>
+          <t>534938</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>522158</t>
+          <t>522788</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>554105</t>
+          <t>556244</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1033871</t>
+          <t>1033559</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1081272</t>
+          <t>1080169</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,38%</t>
         </is>
       </c>
     </row>
@@ -10707,7 +10707,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4064</t>
+          <t>4740</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3015</t>
+          <t>2956</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>587</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5651</t>
+          <t>5074</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>19,4%</t>
         </is>
       </c>
     </row>
@@ -10815,7 +10815,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>7351</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -10850,7 +10850,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11049</t>
+          <t>11108</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20504</t>
+          <t>21081</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25563</t>
+          <t>25568</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,76%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>418</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4681</t>
+          <t>4654</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>722</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3983</t>
+          <t>4589</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7028</t>
+          <t>7123</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,77%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8948</t>
+          <t>8975</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13223</t>
+          <t>13211</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12347</t>
+          <t>11741</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15659</t>
+          <t>15608</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22931</t>
+          <t>22836</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>28126</t>
+          <t>28106</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,81%</t>
         </is>
       </c>
     </row>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4587</t>
+          <t>3393</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11408,7 +11408,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>385</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4494</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>680</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6006</t>
+          <t>5625</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -11501,7 +11501,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9370</t>
+          <t>10564</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11928</t>
+          <t>11621</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16091</t>
+          <t>16037</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>24373</t>
+          <t>24754</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>29706</t>
+          <t>29699</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,76%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7840</t>
+          <t>7790</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3578</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10465</t>
+          <t>10175</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>36,39%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5428</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11975</t>
+          <t>11646</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11117</t>
+          <t>11120</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -11894,7 +11894,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17498</t>
+          <t>17788</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25980</t>
+          <t>25741</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,06%</t>
         </is>
       </c>
     </row>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2905</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3857</t>
+          <t>3197</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>34,29%</t>
         </is>
       </c>
     </row>
@@ -12222,7 +12222,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2452</t>
+          <t>2428</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -12257,7 +12257,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5467</t>
+          <t>6127</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2387</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6107</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>1470</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6696</t>
+          <t>6334</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>24,19%</t>
         </is>
       </c>
     </row>
@@ -12530,7 +12530,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6746</t>
+          <t>6650</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -12545,7 +12545,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10948</t>
+          <t>11413</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16112</t>
+          <t>15996</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>19492</t>
+          <t>19854</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>24764</t>
+          <t>24718</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>1409</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8073</t>
+          <t>7942</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2730</t>
+          <t>2457</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10489</t>
+          <t>10407</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5445</t>
+          <t>5245</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15432</t>
+          <t>15716</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>31,42%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14218</t>
+          <t>14349</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20789</t>
+          <t>20882</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>17237</t>
+          <t>17319</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>24996</t>
+          <t>25269</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>34585</t>
+          <t>34301</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>44572</t>
+          <t>44772</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,51%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3574</t>
+          <t>3692</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8721</t>
+          <t>8978</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6260</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13719</t>
+          <t>13626</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11666</t>
+          <t>11617</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20460</t>
+          <t>20935</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>65,59%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8404</t>
+          <t>8286</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>6316</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13682</t>
+          <t>13371</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>11460</t>
+          <t>10985</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>20254</t>
+          <t>20303</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,61%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>13530</t>
+          <t>13605</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26299</t>
+          <t>26560</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>17947</t>
+          <t>18472</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>33365</t>
+          <t>32847</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>35401</t>
+          <t>34095</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>54582</t>
+          <t>54546</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>74015</t>
+          <t>73754</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>86784</t>
+          <t>86709</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>98227</t>
+          <t>98745</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>113645</t>
+          <t>113120</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>177324</t>
+          <t>177360</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>196505</t>
+          <t>197811</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>85,3%</t>
         </is>
       </c>
     </row>
